--- a/artfynd/A 50720-2021 artfynd.xlsx
+++ b/artfynd/A 50720-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50720-2021 artfynd.xlsx
+++ b/artfynd/A 50720-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,6 +1156,131 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127865671</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Åsgatan, 387 95 Borgholms kommun, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608155</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6301615</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bredsätra</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50720-2021 artfynd.xlsx
+++ b/artfynd/A 50720-2021 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>127865671</v>
       </c>
       <c r="B6" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50720-2021 artfynd.xlsx
+++ b/artfynd/A 50720-2021 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>127865671</v>
       </c>
       <c r="B6" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50720-2021 artfynd.xlsx
+++ b/artfynd/A 50720-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84298087</v>
+        <v>84298086</v>
       </c>
       <c r="B2" t="n">
-        <v>101731</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1852</v>
+        <v>981</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grådådra</t>
+          <t>Vit sminkrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alyssum alyssoides</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
+          <t>Buglossoides arvensis var. arvensis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -719,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608093.4671644913</v>
+        <v>608093</v>
       </c>
       <c r="R2" t="n">
-        <v>6301634.907200966</v>
+        <v>6301635</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +743,9 @@
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,41 +774,46 @@
           <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84298092</v>
+        <v>84298087</v>
       </c>
       <c r="B3" t="n">
-        <v>88839</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1000938</v>
+        <v>1852</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grådådra</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Alyssum alyssoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608093.4671644913</v>
+        <v>608093</v>
       </c>
       <c r="R3" t="n">
-        <v>6301634.907200966</v>
+        <v>6301635</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,24 +854,9 @@
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>saknar rökboll, ej bestämbar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,57 +885,70 @@
           <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84298086</v>
+        <v>127865671</v>
       </c>
       <c r="B4" t="n">
-        <v>103493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>981</v>
+        <v>100053</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vit sminkrot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buglossoides arvensis var. arvensis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skedås, Öl</t>
+          <t>Åsgatan, 387 95 Borgholms kommun, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608093.4671644913</v>
+        <v>608155</v>
       </c>
       <c r="R4" t="n">
-        <v>6301634.907200966</v>
+        <v>6301615</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,39 +996,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>sandig betesmark, delvis bränd och röjd/i mur</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>86938934</v>
       </c>
       <c r="B5" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608133.3897691014</v>
+        <v>608133</v>
       </c>
       <c r="R5" t="n">
-        <v>6301638.677116607</v>
+        <v>6301639</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1113,19 +1090,9 @@
           <t>2020-07-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,66 +1121,59 @@
           <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127865671</v>
+        <v>84298092</v>
       </c>
       <c r="B6" t="n">
-        <v>56620</v>
+        <v>91316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100053</v>
+        <v>1000938</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Jordstjärnesläktet</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsgatan, 387 95 Borgholms kommun, Öl</t>
+          <t>Skedås, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608155</v>
+        <v>608093</v>
       </c>
       <c r="R6" t="n">
-        <v>6301615</v>
+        <v>6301635</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,22 +1197,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>05:26</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>05:26</t>
+          <t>2020-04-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>saknar rökboll, ej bestämbar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,25 +1216,27 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sandig betesmark, delvis bränd och röjd/i mur</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50720-2021 artfynd.xlsx
+++ b/artfynd/A 50720-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84298086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84298087</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127865671</t>
         </is>
       </c>
     </row>
@@ -1126,6 +1146,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86938934</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84298092</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>